--- a/T6_PopularGraphs/spotify.xlsx
+++ b/T6_PopularGraphs/spotify.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alanrvazquez/GitHub/TEC-IN2039/Session_7_Multivariate_Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alanvazquez/Documents/GitHub/TEC-IN2039-EN/T6_PopularGraphs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CA868C1-C5A8-DD46-974F-7CE810AD6052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCFF80C-1C37-5F49-A37A-3C390829ADBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{790A01F2-2581-F64E-AC8C-73C3BCB7912C}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="20580" windowHeight="11660" xr2:uid="{790A01F2-2581-F64E-AC8C-73C3BCB7912C}"/>
   </bookViews>
   <sheets>
     <sheet name="spotify_full" sheetId="1" r:id="rId1"/>
@@ -524,10 +524,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -905,6 +904,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B567E7E-99D2-F44E-8062-BA24F9902D3F}">
   <dimension ref="A1:G367"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -933,7 +941,7 @@
       <c r="A2" s="1">
         <v>42741</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
@@ -944,7 +952,7 @@
       <c r="A3" s="1">
         <v>42742</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3">
         <v>2</v>
       </c>
       <c r="C3">
@@ -955,7 +963,7 @@
       <c r="A4" s="1">
         <v>42743</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4">
         <v>3</v>
       </c>
       <c r="C4">
@@ -966,7 +974,7 @@
       <c r="A5" s="1">
         <v>42744</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5">
         <v>4</v>
       </c>
       <c r="C5">
@@ -977,7 +985,7 @@
       <c r="A6" s="1">
         <v>42745</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <v>5</v>
       </c>
       <c r="C6">
@@ -988,7 +996,7 @@
       <c r="A7" s="1">
         <v>42746</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7">
         <v>6</v>
       </c>
       <c r="C7">
@@ -999,7 +1007,7 @@
       <c r="A8" s="1">
         <v>42747</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8">
         <v>7</v>
       </c>
       <c r="C8">
@@ -1010,7 +1018,7 @@
       <c r="A9" s="1">
         <v>42748</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9">
         <v>8</v>
       </c>
       <c r="C9">
@@ -1024,7 +1032,7 @@
       <c r="A10" s="1">
         <v>42749</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10">
         <v>9</v>
       </c>
       <c r="C10">
@@ -1038,7 +1046,7 @@
       <c r="A11" s="1">
         <v>42750</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11">
         <v>10</v>
       </c>
       <c r="C11">
@@ -1052,7 +1060,7 @@
       <c r="A12" s="1">
         <v>42751</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12">
         <v>11</v>
       </c>
       <c r="C12">
@@ -1066,7 +1074,7 @@
       <c r="A13" s="1">
         <v>42752</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13">
         <v>12</v>
       </c>
       <c r="C13">
@@ -1080,7 +1088,7 @@
       <c r="A14" s="1">
         <v>42753</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14">
         <v>13</v>
       </c>
       <c r="C14">
@@ -1094,7 +1102,7 @@
       <c r="A15" s="1">
         <v>42754</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15">
         <v>14</v>
       </c>
       <c r="C15">
@@ -1108,7 +1116,7 @@
       <c r="A16" s="1">
         <v>42755</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16">
         <v>15</v>
       </c>
       <c r="C16">
@@ -1122,7 +1130,7 @@
       <c r="A17" s="1">
         <v>42756</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17">
         <v>16</v>
       </c>
       <c r="C17">
@@ -1136,7 +1144,7 @@
       <c r="A18" s="1">
         <v>42757</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18">
         <v>17</v>
       </c>
       <c r="C18">
@@ -1150,7 +1158,7 @@
       <c r="A19" s="1">
         <v>42758</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19">
         <v>18</v>
       </c>
       <c r="C19">
@@ -1164,7 +1172,7 @@
       <c r="A20" s="1">
         <v>42759</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20">
         <v>19</v>
       </c>
       <c r="C20">
@@ -1178,7 +1186,7 @@
       <c r="A21" s="1">
         <v>42760</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21">
         <v>20</v>
       </c>
       <c r="C21">
@@ -1192,7 +1200,7 @@
       <c r="A22" s="1">
         <v>42761</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22">
         <v>21</v>
       </c>
       <c r="C22">
@@ -1206,7 +1214,7 @@
       <c r="A23" s="1">
         <v>42762</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23">
         <v>22</v>
       </c>
       <c r="C23">
@@ -1220,7 +1228,7 @@
       <c r="A24" s="1">
         <v>42763</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24">
         <v>23</v>
       </c>
       <c r="C24">
@@ -1234,7 +1242,7 @@
       <c r="A25" s="1">
         <v>42764</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25">
         <v>24</v>
       </c>
       <c r="C25">
@@ -1248,7 +1256,7 @@
       <c r="A26" s="1">
         <v>42765</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26">
         <v>25</v>
       </c>
       <c r="C26">
@@ -1262,7 +1270,7 @@
       <c r="A27" s="1">
         <v>42766</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27">
         <v>26</v>
       </c>
       <c r="C27">
@@ -1276,7 +1284,7 @@
       <c r="A28" s="1">
         <v>42767</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28">
         <v>27</v>
       </c>
       <c r="C28">
@@ -1290,7 +1298,7 @@
       <c r="A29" s="1">
         <v>42768</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29">
         <v>28</v>
       </c>
       <c r="C29">
@@ -1304,7 +1312,7 @@
       <c r="A30" s="1">
         <v>42769</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30">
         <v>29</v>
       </c>
       <c r="C30">
@@ -1318,7 +1326,7 @@
       <c r="A31" s="1">
         <v>42770</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31">
         <v>30</v>
       </c>
       <c r="C31">
@@ -1332,7 +1340,7 @@
       <c r="A32" s="1">
         <v>42771</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32">
         <v>31</v>
       </c>
       <c r="C32">
@@ -1346,7 +1354,7 @@
       <c r="A33" s="1">
         <v>42772</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33">
         <v>32</v>
       </c>
       <c r="C33">
@@ -1360,7 +1368,7 @@
       <c r="A34" s="1">
         <v>42773</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34">
         <v>33</v>
       </c>
       <c r="C34">
@@ -1374,7 +1382,7 @@
       <c r="A35" s="1">
         <v>42774</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35">
         <v>34</v>
       </c>
       <c r="C35">
@@ -1388,7 +1396,7 @@
       <c r="A36" s="1">
         <v>42775</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36">
         <v>35</v>
       </c>
       <c r="C36">
@@ -1402,7 +1410,7 @@
       <c r="A37" s="1">
         <v>42776</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37">
         <v>36</v>
       </c>
       <c r="C37">
@@ -1416,7 +1424,7 @@
       <c r="A38" s="1">
         <v>42777</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38">
         <v>37</v>
       </c>
       <c r="C38">
@@ -1430,7 +1438,7 @@
       <c r="A39" s="1">
         <v>42778</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39">
         <v>38</v>
       </c>
       <c r="C39">
@@ -1444,7 +1452,7 @@
       <c r="A40" s="1">
         <v>42779</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40">
         <v>39</v>
       </c>
       <c r="C40">
@@ -1458,7 +1466,7 @@
       <c r="A41" s="1">
         <v>42780</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41">
         <v>40</v>
       </c>
       <c r="C41">
@@ -1472,7 +1480,7 @@
       <c r="A42" s="1">
         <v>42781</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42">
         <v>41</v>
       </c>
       <c r="C42">
@@ -1486,7 +1494,7 @@
       <c r="A43" s="1">
         <v>42782</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43">
         <v>42</v>
       </c>
       <c r="C43">
@@ -1500,7 +1508,7 @@
       <c r="A44" s="1">
         <v>42783</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44">
         <v>43</v>
       </c>
       <c r="C44">
@@ -1514,7 +1522,7 @@
       <c r="A45" s="1">
         <v>42784</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45">
         <v>44</v>
       </c>
       <c r="C45">
@@ -1528,7 +1536,7 @@
       <c r="A46" s="1">
         <v>42785</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46">
         <v>45</v>
       </c>
       <c r="C46">
@@ -1542,7 +1550,7 @@
       <c r="A47" s="1">
         <v>42786</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47">
         <v>46</v>
       </c>
       <c r="C47">
@@ -1556,7 +1564,7 @@
       <c r="A48" s="1">
         <v>42787</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48">
         <v>47</v>
       </c>
       <c r="C48">
@@ -1570,7 +1578,7 @@
       <c r="A49" s="1">
         <v>42788</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49">
         <v>48</v>
       </c>
       <c r="C49">
@@ -1587,7 +1595,7 @@
       <c r="A50" s="1">
         <v>42789</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50">
         <v>49</v>
       </c>
       <c r="C50">
@@ -1604,7 +1612,7 @@
       <c r="A51" s="1">
         <v>42790</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51">
         <v>50</v>
       </c>
       <c r="C51">
@@ -1621,7 +1629,7 @@
       <c r="A52" s="1">
         <v>42791</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52">
         <v>51</v>
       </c>
       <c r="C52">
@@ -1638,7 +1646,7 @@
       <c r="A53" s="1">
         <v>42792</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53">
         <v>52</v>
       </c>
       <c r="C53">
@@ -1655,7 +1663,7 @@
       <c r="A54" s="1">
         <v>42793</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54">
         <v>53</v>
       </c>
       <c r="C54">
@@ -1672,7 +1680,7 @@
       <c r="A55" s="1">
         <v>42794</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55">
         <v>54</v>
       </c>
       <c r="C55">
@@ -1689,7 +1697,7 @@
       <c r="A56" s="1">
         <v>42795</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56">
         <v>55</v>
       </c>
       <c r="C56">
@@ -1706,7 +1714,7 @@
       <c r="A57" s="1">
         <v>42796</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57">
         <v>56</v>
       </c>
       <c r="C57">
@@ -1723,7 +1731,7 @@
       <c r="A58" s="1">
         <v>42797</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58">
         <v>57</v>
       </c>
       <c r="C58">
@@ -1740,7 +1748,7 @@
       <c r="A59" s="1">
         <v>42798</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59">
         <v>58</v>
       </c>
       <c r="C59">
@@ -1757,7 +1765,7 @@
       <c r="A60" s="1">
         <v>42799</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60">
         <v>59</v>
       </c>
       <c r="C60">
@@ -1774,7 +1782,7 @@
       <c r="A61" s="1">
         <v>42800</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61">
         <v>60</v>
       </c>
       <c r="C61">
@@ -1791,7 +1799,7 @@
       <c r="A62" s="1">
         <v>42801</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62">
         <v>61</v>
       </c>
       <c r="C62">
@@ -1808,7 +1816,7 @@
       <c r="A63" s="1">
         <v>42802</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63">
         <v>62</v>
       </c>
       <c r="C63">
@@ -1825,7 +1833,7 @@
       <c r="A64" s="1">
         <v>42803</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64">
         <v>63</v>
       </c>
       <c r="C64">
@@ -1842,7 +1850,7 @@
       <c r="A65" s="1">
         <v>42804</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65">
         <v>64</v>
       </c>
       <c r="C65">
@@ -1859,7 +1867,7 @@
       <c r="A66" s="1">
         <v>42805</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66">
         <v>65</v>
       </c>
       <c r="C66">
@@ -1876,7 +1884,7 @@
       <c r="A67" s="1">
         <v>42806</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67">
         <v>66</v>
       </c>
       <c r="C67">
@@ -1893,7 +1901,7 @@
       <c r="A68" s="1">
         <v>42807</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68">
         <v>67</v>
       </c>
       <c r="C68">
@@ -1910,7 +1918,7 @@
       <c r="A69" s="1">
         <v>42808</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69">
         <v>68</v>
       </c>
       <c r="C69">
@@ -1927,7 +1935,7 @@
       <c r="A70" s="1">
         <v>42809</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70">
         <v>69</v>
       </c>
       <c r="C70">
@@ -1944,7 +1952,7 @@
       <c r="A71" s="1">
         <v>42810</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71">
         <v>70</v>
       </c>
       <c r="C71">
@@ -1961,7 +1969,7 @@
       <c r="A72" s="1">
         <v>42811</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72">
         <v>71</v>
       </c>
       <c r="C72">
@@ -1978,7 +1986,7 @@
       <c r="A73" s="1">
         <v>42812</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B73">
         <v>72</v>
       </c>
       <c r="C73">
@@ -1995,7 +2003,7 @@
       <c r="A74" s="1">
         <v>42813</v>
       </c>
-      <c r="B74" s="2">
+      <c r="B74">
         <v>73</v>
       </c>
       <c r="C74">
@@ -2012,7 +2020,7 @@
       <c r="A75" s="1">
         <v>42814</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75">
         <v>74</v>
       </c>
       <c r="C75">
@@ -2029,7 +2037,7 @@
       <c r="A76" s="1">
         <v>42815</v>
       </c>
-      <c r="B76" s="2">
+      <c r="B76">
         <v>75</v>
       </c>
       <c r="C76">
@@ -2046,7 +2054,7 @@
       <c r="A77" s="1">
         <v>42816</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77">
         <v>76</v>
       </c>
       <c r="C77">
@@ -2063,7 +2071,7 @@
       <c r="A78" s="1">
         <v>42817</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78">
         <v>77</v>
       </c>
       <c r="C78">
@@ -2080,7 +2088,7 @@
       <c r="A79" s="1">
         <v>42818</v>
       </c>
-      <c r="B79" s="2">
+      <c r="B79">
         <v>78</v>
       </c>
       <c r="C79">
@@ -2097,7 +2105,7 @@
       <c r="A80" s="1">
         <v>42819</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B80">
         <v>79</v>
       </c>
       <c r="C80">
@@ -2114,7 +2122,7 @@
       <c r="A81" s="1">
         <v>42820</v>
       </c>
-      <c r="B81" s="2">
+      <c r="B81">
         <v>80</v>
       </c>
       <c r="C81">
@@ -2131,7 +2139,7 @@
       <c r="A82" s="1">
         <v>42821</v>
       </c>
-      <c r="B82" s="2">
+      <c r="B82">
         <v>81</v>
       </c>
       <c r="C82">
@@ -2148,7 +2156,7 @@
       <c r="A83" s="1">
         <v>42822</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83">
         <v>82</v>
       </c>
       <c r="C83">
@@ -2165,7 +2173,7 @@
       <c r="A84" s="1">
         <v>42823</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84">
         <v>83</v>
       </c>
       <c r="C84">
@@ -2182,7 +2190,7 @@
       <c r="A85" s="1">
         <v>42824</v>
       </c>
-      <c r="B85" s="2">
+      <c r="B85">
         <v>84</v>
       </c>
       <c r="C85">
@@ -2199,7 +2207,7 @@
       <c r="A86" s="1">
         <v>42825</v>
       </c>
-      <c r="B86" s="2">
+      <c r="B86">
         <v>85</v>
       </c>
       <c r="C86">
@@ -2219,7 +2227,7 @@
       <c r="A87" s="1">
         <v>42826</v>
       </c>
-      <c r="B87" s="2">
+      <c r="B87">
         <v>86</v>
       </c>
       <c r="C87">
@@ -2239,7 +2247,7 @@
       <c r="A88" s="1">
         <v>42827</v>
       </c>
-      <c r="B88" s="2">
+      <c r="B88">
         <v>87</v>
       </c>
       <c r="C88">
@@ -2259,7 +2267,7 @@
       <c r="A89" s="1">
         <v>42828</v>
       </c>
-      <c r="B89" s="2">
+      <c r="B89">
         <v>88</v>
       </c>
       <c r="C89">
@@ -2279,7 +2287,7 @@
       <c r="A90" s="1">
         <v>42829</v>
       </c>
-      <c r="B90" s="2">
+      <c r="B90">
         <v>89</v>
       </c>
       <c r="C90">
@@ -2299,7 +2307,7 @@
       <c r="A91" s="1">
         <v>42830</v>
       </c>
-      <c r="B91" s="2">
+      <c r="B91">
         <v>90</v>
       </c>
       <c r="C91">
@@ -2319,7 +2327,7 @@
       <c r="A92" s="1">
         <v>42831</v>
       </c>
-      <c r="B92" s="2">
+      <c r="B92">
         <v>91</v>
       </c>
       <c r="C92">
@@ -2339,7 +2347,7 @@
       <c r="A93" s="1">
         <v>42832</v>
       </c>
-      <c r="B93" s="2">
+      <c r="B93">
         <v>92</v>
       </c>
       <c r="C93">
@@ -2362,7 +2370,7 @@
       <c r="A94" s="1">
         <v>42833</v>
       </c>
-      <c r="B94" s="2">
+      <c r="B94">
         <v>93</v>
       </c>
       <c r="C94">
@@ -2385,7 +2393,7 @@
       <c r="A95" s="1">
         <v>42834</v>
       </c>
-      <c r="B95" s="2">
+      <c r="B95">
         <v>94</v>
       </c>
       <c r="C95">
@@ -2408,7 +2416,7 @@
       <c r="A96" s="1">
         <v>42835</v>
       </c>
-      <c r="B96" s="2">
+      <c r="B96">
         <v>95</v>
       </c>
       <c r="C96">
@@ -2431,7 +2439,7 @@
       <c r="A97" s="1">
         <v>42836</v>
       </c>
-      <c r="B97" s="2">
+      <c r="B97">
         <v>96</v>
       </c>
       <c r="C97">
@@ -2454,7 +2462,7 @@
       <c r="A98" s="1">
         <v>42837</v>
       </c>
-      <c r="B98" s="2">
+      <c r="B98">
         <v>97</v>
       </c>
       <c r="C98">
@@ -2477,7 +2485,7 @@
       <c r="A99" s="1">
         <v>42838</v>
       </c>
-      <c r="B99" s="2">
+      <c r="B99">
         <v>98</v>
       </c>
       <c r="C99">
@@ -2500,7 +2508,7 @@
       <c r="A100" s="1">
         <v>42839</v>
       </c>
-      <c r="B100" s="2">
+      <c r="B100">
         <v>99</v>
       </c>
       <c r="C100">
@@ -2523,7 +2531,7 @@
       <c r="A101" s="1">
         <v>42840</v>
       </c>
-      <c r="B101" s="2">
+      <c r="B101">
         <v>100</v>
       </c>
       <c r="C101">
@@ -2546,7 +2554,7 @@
       <c r="A102" s="1">
         <v>42841</v>
       </c>
-      <c r="B102" s="2">
+      <c r="B102">
         <v>101</v>
       </c>
       <c r="C102">
@@ -2569,7 +2577,7 @@
       <c r="A103" s="1">
         <v>42842</v>
       </c>
-      <c r="B103" s="2">
+      <c r="B103">
         <v>102</v>
       </c>
       <c r="C103">
@@ -2592,7 +2600,7 @@
       <c r="A104" s="1">
         <v>42843</v>
       </c>
-      <c r="B104" s="2">
+      <c r="B104">
         <v>103</v>
       </c>
       <c r="C104">
@@ -2615,7 +2623,7 @@
       <c r="A105" s="1">
         <v>42844</v>
       </c>
-      <c r="B105" s="2">
+      <c r="B105">
         <v>104</v>
       </c>
       <c r="C105">
@@ -2638,7 +2646,7 @@
       <c r="A106" s="1">
         <v>42845</v>
       </c>
-      <c r="B106" s="2">
+      <c r="B106">
         <v>105</v>
       </c>
       <c r="C106">
@@ -2661,7 +2669,7 @@
       <c r="A107" s="1">
         <v>42846</v>
       </c>
-      <c r="B107" s="2">
+      <c r="B107">
         <v>106</v>
       </c>
       <c r="C107">
@@ -2684,7 +2692,7 @@
       <c r="A108" s="1">
         <v>42847</v>
       </c>
-      <c r="B108" s="2">
+      <c r="B108">
         <v>107</v>
       </c>
       <c r="C108">
@@ -2707,7 +2715,7 @@
       <c r="A109" s="1">
         <v>42848</v>
       </c>
-      <c r="B109" s="2">
+      <c r="B109">
         <v>108</v>
       </c>
       <c r="C109">
@@ -2730,7 +2738,7 @@
       <c r="A110" s="1">
         <v>42849</v>
       </c>
-      <c r="B110" s="2">
+      <c r="B110">
         <v>109</v>
       </c>
       <c r="C110">
@@ -2753,7 +2761,7 @@
       <c r="A111" s="1">
         <v>42850</v>
       </c>
-      <c r="B111" s="2">
+      <c r="B111">
         <v>110</v>
       </c>
       <c r="C111">
@@ -2776,7 +2784,7 @@
       <c r="A112" s="1">
         <v>42851</v>
       </c>
-      <c r="B112" s="2">
+      <c r="B112">
         <v>111</v>
       </c>
       <c r="C112">
@@ -2799,7 +2807,7 @@
       <c r="A113" s="1">
         <v>42852</v>
       </c>
-      <c r="B113" s="2">
+      <c r="B113">
         <v>112</v>
       </c>
       <c r="C113">
@@ -2822,7 +2830,7 @@
       <c r="A114" s="1">
         <v>42853</v>
       </c>
-      <c r="B114" s="2">
+      <c r="B114">
         <v>113</v>
       </c>
       <c r="C114">
@@ -2845,7 +2853,7 @@
       <c r="A115" s="1">
         <v>42854</v>
       </c>
-      <c r="B115" s="2">
+      <c r="B115">
         <v>114</v>
       </c>
       <c r="C115">
@@ -2868,7 +2876,7 @@
       <c r="A116" s="1">
         <v>42855</v>
       </c>
-      <c r="B116" s="2">
+      <c r="B116">
         <v>115</v>
       </c>
       <c r="C116">
@@ -2891,7 +2899,7 @@
       <c r="A117" s="1">
         <v>42856</v>
       </c>
-      <c r="B117" s="2">
+      <c r="B117">
         <v>116</v>
       </c>
       <c r="C117">
@@ -2914,7 +2922,7 @@
       <c r="A118" s="1">
         <v>42857</v>
       </c>
-      <c r="B118" s="2">
+      <c r="B118">
         <v>117</v>
       </c>
       <c r="C118">
@@ -2937,7 +2945,7 @@
       <c r="A119" s="1">
         <v>42858</v>
       </c>
-      <c r="B119" s="2">
+      <c r="B119">
         <v>118</v>
       </c>
       <c r="C119">
@@ -2960,7 +2968,7 @@
       <c r="A120" s="1">
         <v>42859</v>
       </c>
-      <c r="B120" s="2">
+      <c r="B120">
         <v>119</v>
       </c>
       <c r="C120">
@@ -2983,7 +2991,7 @@
       <c r="A121" s="1">
         <v>42860</v>
       </c>
-      <c r="B121" s="2">
+      <c r="B121">
         <v>120</v>
       </c>
       <c r="C121">
@@ -3006,7 +3014,7 @@
       <c r="A122" s="1">
         <v>42861</v>
       </c>
-      <c r="B122" s="2">
+      <c r="B122">
         <v>121</v>
       </c>
       <c r="C122">
@@ -3029,7 +3037,7 @@
       <c r="A123" s="1">
         <v>42862</v>
       </c>
-      <c r="B123" s="2">
+      <c r="B123">
         <v>122</v>
       </c>
       <c r="C123">
@@ -3052,7 +3060,7 @@
       <c r="A124" s="1">
         <v>42863</v>
       </c>
-      <c r="B124" s="2">
+      <c r="B124">
         <v>123</v>
       </c>
       <c r="C124">
@@ -3075,7 +3083,7 @@
       <c r="A125" s="1">
         <v>42864</v>
       </c>
-      <c r="B125" s="2">
+      <c r="B125">
         <v>124</v>
       </c>
       <c r="C125">
@@ -3098,7 +3106,7 @@
       <c r="A126" s="1">
         <v>42865</v>
       </c>
-      <c r="B126" s="2">
+      <c r="B126">
         <v>125</v>
       </c>
       <c r="C126">
@@ -3121,7 +3129,7 @@
       <c r="A127" s="1">
         <v>42866</v>
       </c>
-      <c r="B127" s="2">
+      <c r="B127">
         <v>126</v>
       </c>
       <c r="C127">
@@ -3144,7 +3152,7 @@
       <c r="A128" s="1">
         <v>42867</v>
       </c>
-      <c r="B128" s="2">
+      <c r="B128">
         <v>127</v>
       </c>
       <c r="C128">
@@ -3167,7 +3175,7 @@
       <c r="A129" s="1">
         <v>42868</v>
       </c>
-      <c r="B129" s="2">
+      <c r="B129">
         <v>128</v>
       </c>
       <c r="C129">
@@ -3190,7 +3198,7 @@
       <c r="A130" s="1">
         <v>42869</v>
       </c>
-      <c r="B130" s="2">
+      <c r="B130">
         <v>129</v>
       </c>
       <c r="C130">
@@ -3213,7 +3221,7 @@
       <c r="A131" s="1">
         <v>42870</v>
       </c>
-      <c r="B131" s="2">
+      <c r="B131">
         <v>130</v>
       </c>
       <c r="C131">
@@ -3236,7 +3244,7 @@
       <c r="A132" s="1">
         <v>42871</v>
       </c>
-      <c r="B132" s="2">
+      <c r="B132">
         <v>131</v>
       </c>
       <c r="C132">
@@ -3259,7 +3267,7 @@
       <c r="A133" s="1">
         <v>42872</v>
       </c>
-      <c r="B133" s="2">
+      <c r="B133">
         <v>132</v>
       </c>
       <c r="C133">
@@ -3282,7 +3290,7 @@
       <c r="A134" s="1">
         <v>42873</v>
       </c>
-      <c r="B134" s="2">
+      <c r="B134">
         <v>133</v>
       </c>
       <c r="C134">
@@ -3305,7 +3313,7 @@
       <c r="A135" s="1">
         <v>42874</v>
       </c>
-      <c r="B135" s="2">
+      <c r="B135">
         <v>134</v>
       </c>
       <c r="C135">
@@ -3328,7 +3336,7 @@
       <c r="A136" s="1">
         <v>42875</v>
       </c>
-      <c r="B136" s="2">
+      <c r="B136">
         <v>135</v>
       </c>
       <c r="C136">
@@ -3351,7 +3359,7 @@
       <c r="A137" s="1">
         <v>42876</v>
       </c>
-      <c r="B137" s="2">
+      <c r="B137">
         <v>136</v>
       </c>
       <c r="C137">
@@ -3374,7 +3382,7 @@
       <c r="A138" s="1">
         <v>42877</v>
       </c>
-      <c r="B138" s="2">
+      <c r="B138">
         <v>137</v>
       </c>
       <c r="C138">
@@ -3397,7 +3405,7 @@
       <c r="A139" s="1">
         <v>42878</v>
       </c>
-      <c r="B139" s="2">
+      <c r="B139">
         <v>138</v>
       </c>
       <c r="C139">
@@ -3420,7 +3428,7 @@
       <c r="A140" s="1">
         <v>42879</v>
       </c>
-      <c r="B140" s="2">
+      <c r="B140">
         <v>139</v>
       </c>
       <c r="C140">
@@ -3443,7 +3451,7 @@
       <c r="A141" s="1">
         <v>42880</v>
       </c>
-      <c r="B141" s="2">
+      <c r="B141">
         <v>140</v>
       </c>
       <c r="C141">
@@ -3466,7 +3474,7 @@
       <c r="A142" s="1">
         <v>42881</v>
       </c>
-      <c r="B142" s="2">
+      <c r="B142">
         <v>141</v>
       </c>
       <c r="C142">
@@ -3489,7 +3497,7 @@
       <c r="A143" s="1">
         <v>42882</v>
       </c>
-      <c r="B143" s="2">
+      <c r="B143">
         <v>142</v>
       </c>
       <c r="C143">
@@ -3512,7 +3520,7 @@
       <c r="A144" s="1">
         <v>42883</v>
       </c>
-      <c r="B144" s="2">
+      <c r="B144">
         <v>143</v>
       </c>
       <c r="C144">
@@ -3535,7 +3543,7 @@
       <c r="A145" s="1">
         <v>42884</v>
       </c>
-      <c r="B145" s="2">
+      <c r="B145">
         <v>144</v>
       </c>
       <c r="C145">
@@ -3558,7 +3566,7 @@
       <c r="A146" s="1">
         <v>42887</v>
       </c>
-      <c r="B146" s="2">
+      <c r="B146">
         <v>145</v>
       </c>
       <c r="C146">
@@ -3581,7 +3589,7 @@
       <c r="A147" s="1">
         <v>42889</v>
       </c>
-      <c r="B147" s="2">
+      <c r="B147">
         <v>146</v>
       </c>
       <c r="C147">
@@ -3604,7 +3612,7 @@
       <c r="A148" s="1">
         <v>42890</v>
       </c>
-      <c r="B148" s="2">
+      <c r="B148">
         <v>147</v>
       </c>
       <c r="C148">
@@ -3627,7 +3635,7 @@
       <c r="A149" s="1">
         <v>42891</v>
       </c>
-      <c r="B149" s="2">
+      <c r="B149">
         <v>148</v>
       </c>
       <c r="C149">
@@ -3650,7 +3658,7 @@
       <c r="A150" s="1">
         <v>42892</v>
       </c>
-      <c r="B150" s="2">
+      <c r="B150">
         <v>149</v>
       </c>
       <c r="C150">
@@ -3673,7 +3681,7 @@
       <c r="A151" s="1">
         <v>42893</v>
       </c>
-      <c r="B151" s="2">
+      <c r="B151">
         <v>150</v>
       </c>
       <c r="C151">
@@ -3696,7 +3704,7 @@
       <c r="A152" s="1">
         <v>42894</v>
       </c>
-      <c r="B152" s="2">
+      <c r="B152">
         <v>151</v>
       </c>
       <c r="C152">
@@ -3719,7 +3727,7 @@
       <c r="A153" s="1">
         <v>42895</v>
       </c>
-      <c r="B153" s="2">
+      <c r="B153">
         <v>152</v>
       </c>
       <c r="C153">
@@ -3742,7 +3750,7 @@
       <c r="A154" s="1">
         <v>42896</v>
       </c>
-      <c r="B154" s="2">
+      <c r="B154">
         <v>153</v>
       </c>
       <c r="C154">
@@ -3765,7 +3773,7 @@
       <c r="A155" s="1">
         <v>42897</v>
       </c>
-      <c r="B155" s="2">
+      <c r="B155">
         <v>154</v>
       </c>
       <c r="C155">
@@ -3788,7 +3796,7 @@
       <c r="A156" s="1">
         <v>42898</v>
       </c>
-      <c r="B156" s="2">
+      <c r="B156">
         <v>155</v>
       </c>
       <c r="C156">
@@ -3811,7 +3819,7 @@
       <c r="A157" s="1">
         <v>42899</v>
       </c>
-      <c r="B157" s="2">
+      <c r="B157">
         <v>156</v>
       </c>
       <c r="C157">
@@ -3834,7 +3842,7 @@
       <c r="A158" s="1">
         <v>42900</v>
       </c>
-      <c r="B158" s="2">
+      <c r="B158">
         <v>157</v>
       </c>
       <c r="C158">
@@ -3857,7 +3865,7 @@
       <c r="A159" s="1">
         <v>42901</v>
       </c>
-      <c r="B159" s="2">
+      <c r="B159">
         <v>158</v>
       </c>
       <c r="C159">
@@ -3880,7 +3888,7 @@
       <c r="A160" s="1">
         <v>42902</v>
       </c>
-      <c r="B160" s="2">
+      <c r="B160">
         <v>159</v>
       </c>
       <c r="C160">
@@ -3903,7 +3911,7 @@
       <c r="A161" s="1">
         <v>42903</v>
       </c>
-      <c r="B161" s="2">
+      <c r="B161">
         <v>160</v>
       </c>
       <c r="C161">
@@ -3926,7 +3934,7 @@
       <c r="A162" s="1">
         <v>42904</v>
       </c>
-      <c r="B162" s="2">
+      <c r="B162">
         <v>161</v>
       </c>
       <c r="C162">
@@ -3949,7 +3957,7 @@
       <c r="A163" s="1">
         <v>42905</v>
       </c>
-      <c r="B163" s="2">
+      <c r="B163">
         <v>162</v>
       </c>
       <c r="C163">
@@ -3972,7 +3980,7 @@
       <c r="A164" s="1">
         <v>42906</v>
       </c>
-      <c r="B164" s="2">
+      <c r="B164">
         <v>163</v>
       </c>
       <c r="C164">
@@ -3995,7 +4003,7 @@
       <c r="A165" s="1">
         <v>42907</v>
       </c>
-      <c r="B165" s="2">
+      <c r="B165">
         <v>164</v>
       </c>
       <c r="C165">
@@ -4018,7 +4026,7 @@
       <c r="A166" s="1">
         <v>42908</v>
       </c>
-      <c r="B166" s="2">
+      <c r="B166">
         <v>165</v>
       </c>
       <c r="C166">
@@ -4041,7 +4049,7 @@
       <c r="A167" s="1">
         <v>42909</v>
       </c>
-      <c r="B167" s="2">
+      <c r="B167">
         <v>166</v>
       </c>
       <c r="C167">
@@ -4064,7 +4072,7 @@
       <c r="A168" s="1">
         <v>42910</v>
       </c>
-      <c r="B168" s="2">
+      <c r="B168">
         <v>167</v>
       </c>
       <c r="C168">
@@ -4087,7 +4095,7 @@
       <c r="A169" s="1">
         <v>42911</v>
       </c>
-      <c r="B169" s="2">
+      <c r="B169">
         <v>168</v>
       </c>
       <c r="C169">
@@ -4110,7 +4118,7 @@
       <c r="A170" s="1">
         <v>42912</v>
       </c>
-      <c r="B170" s="2">
+      <c r="B170">
         <v>169</v>
       </c>
       <c r="C170">
@@ -4133,7 +4141,7 @@
       <c r="A171" s="1">
         <v>42913</v>
       </c>
-      <c r="B171" s="2">
+      <c r="B171">
         <v>170</v>
       </c>
       <c r="C171">
@@ -4156,7 +4164,7 @@
       <c r="A172" s="1">
         <v>42914</v>
       </c>
-      <c r="B172" s="2">
+      <c r="B172">
         <v>171</v>
       </c>
       <c r="C172">
@@ -4179,7 +4187,7 @@
       <c r="A173" s="1">
         <v>42915</v>
       </c>
-      <c r="B173" s="2">
+      <c r="B173">
         <v>172</v>
       </c>
       <c r="C173">
@@ -4202,7 +4210,7 @@
       <c r="A174" s="1">
         <v>42916</v>
       </c>
-      <c r="B174" s="2">
+      <c r="B174">
         <v>173</v>
       </c>
       <c r="C174">
@@ -4225,7 +4233,7 @@
       <c r="A175" s="1">
         <v>42917</v>
       </c>
-      <c r="B175" s="2">
+      <c r="B175">
         <v>174</v>
       </c>
       <c r="C175">
@@ -4248,7 +4256,7 @@
       <c r="A176" s="1">
         <v>42918</v>
       </c>
-      <c r="B176" s="2">
+      <c r="B176">
         <v>175</v>
       </c>
       <c r="C176">
@@ -4271,7 +4279,7 @@
       <c r="A177" s="1">
         <v>42919</v>
       </c>
-      <c r="B177" s="2">
+      <c r="B177">
         <v>176</v>
       </c>
       <c r="C177">
@@ -4294,7 +4302,7 @@
       <c r="A178" s="1">
         <v>42920</v>
       </c>
-      <c r="B178" s="2">
+      <c r="B178">
         <v>177</v>
       </c>
       <c r="C178">
@@ -4317,7 +4325,7 @@
       <c r="A179" s="1">
         <v>42921</v>
       </c>
-      <c r="B179" s="2">
+      <c r="B179">
         <v>178</v>
       </c>
       <c r="C179">
@@ -4340,7 +4348,7 @@
       <c r="A180" s="1">
         <v>42922</v>
       </c>
-      <c r="B180" s="2">
+      <c r="B180">
         <v>179</v>
       </c>
       <c r="C180">
@@ -4363,7 +4371,7 @@
       <c r="A181" s="1">
         <v>42923</v>
       </c>
-      <c r="B181" s="2">
+      <c r="B181">
         <v>180</v>
       </c>
       <c r="C181">
@@ -4386,7 +4394,7 @@
       <c r="A182" s="1">
         <v>42924</v>
       </c>
-      <c r="B182" s="2">
+      <c r="B182">
         <v>181</v>
       </c>
       <c r="C182">
@@ -4409,7 +4417,7 @@
       <c r="A183" s="1">
         <v>42925</v>
       </c>
-      <c r="B183" s="2">
+      <c r="B183">
         <v>182</v>
       </c>
       <c r="C183">
@@ -4432,7 +4440,7 @@
       <c r="A184" s="1">
         <v>42926</v>
       </c>
-      <c r="B184" s="2">
+      <c r="B184">
         <v>183</v>
       </c>
       <c r="C184">
@@ -4455,7 +4463,7 @@
       <c r="A185" s="1">
         <v>42927</v>
       </c>
-      <c r="B185" s="2">
+      <c r="B185">
         <v>184</v>
       </c>
       <c r="C185">
@@ -4478,7 +4486,7 @@
       <c r="A186" s="1">
         <v>42928</v>
       </c>
-      <c r="B186" s="2">
+      <c r="B186">
         <v>185</v>
       </c>
       <c r="C186">
@@ -4501,7 +4509,7 @@
       <c r="A187" s="1">
         <v>42929</v>
       </c>
-      <c r="B187" s="2">
+      <c r="B187">
         <v>186</v>
       </c>
       <c r="C187">
@@ -4524,7 +4532,7 @@
       <c r="A188" s="1">
         <v>42930</v>
       </c>
-      <c r="B188" s="2">
+      <c r="B188">
         <v>187</v>
       </c>
       <c r="C188">
@@ -4547,7 +4555,7 @@
       <c r="A189" s="1">
         <v>42931</v>
       </c>
-      <c r="B189" s="2">
+      <c r="B189">
         <v>188</v>
       </c>
       <c r="C189">
@@ -4570,7 +4578,7 @@
       <c r="A190" s="1">
         <v>42932</v>
       </c>
-      <c r="B190" s="2">
+      <c r="B190">
         <v>189</v>
       </c>
       <c r="C190">
@@ -4593,7 +4601,7 @@
       <c r="A191" s="1">
         <v>42933</v>
       </c>
-      <c r="B191" s="2">
+      <c r="B191">
         <v>190</v>
       </c>
       <c r="C191">
@@ -4616,7 +4624,7 @@
       <c r="A192" s="1">
         <v>42934</v>
       </c>
-      <c r="B192" s="2">
+      <c r="B192">
         <v>191</v>
       </c>
       <c r="C192">
@@ -4639,7 +4647,7 @@
       <c r="A193" s="1">
         <v>42935</v>
       </c>
-      <c r="B193" s="2">
+      <c r="B193">
         <v>192</v>
       </c>
       <c r="C193">
@@ -4662,7 +4670,7 @@
       <c r="A194" s="1">
         <v>42936</v>
       </c>
-      <c r="B194" s="2">
+      <c r="B194">
         <v>193</v>
       </c>
       <c r="C194">
@@ -4685,7 +4693,7 @@
       <c r="A195" s="1">
         <v>42937</v>
       </c>
-      <c r="B195" s="2">
+      <c r="B195">
         <v>194</v>
       </c>
       <c r="C195">
@@ -4708,7 +4716,7 @@
       <c r="A196" s="1">
         <v>42938</v>
       </c>
-      <c r="B196" s="2">
+      <c r="B196">
         <v>195</v>
       </c>
       <c r="C196">
@@ -4731,7 +4739,7 @@
       <c r="A197" s="1">
         <v>42939</v>
       </c>
-      <c r="B197" s="2">
+      <c r="B197">
         <v>196</v>
       </c>
       <c r="C197">
@@ -4754,7 +4762,7 @@
       <c r="A198" s="1">
         <v>42940</v>
       </c>
-      <c r="B198" s="2">
+      <c r="B198">
         <v>197</v>
       </c>
       <c r="C198">
@@ -4777,7 +4785,7 @@
       <c r="A199" s="1">
         <v>42941</v>
       </c>
-      <c r="B199" s="2">
+      <c r="B199">
         <v>198</v>
       </c>
       <c r="C199">
@@ -4800,7 +4808,7 @@
       <c r="A200" s="1">
         <v>42942</v>
       </c>
-      <c r="B200" s="2">
+      <c r="B200">
         <v>199</v>
       </c>
       <c r="C200">
@@ -4823,7 +4831,7 @@
       <c r="A201" s="1">
         <v>42943</v>
       </c>
-      <c r="B201" s="2">
+      <c r="B201">
         <v>200</v>
       </c>
       <c r="C201">
@@ -4846,7 +4854,7 @@
       <c r="A202" s="1">
         <v>42944</v>
       </c>
-      <c r="B202" s="2">
+      <c r="B202">
         <v>201</v>
       </c>
       <c r="C202">
@@ -4869,7 +4877,7 @@
       <c r="A203" s="1">
         <v>42945</v>
       </c>
-      <c r="B203" s="2">
+      <c r="B203">
         <v>202</v>
       </c>
       <c r="C203">
@@ -4892,7 +4900,7 @@
       <c r="A204" s="1">
         <v>42946</v>
       </c>
-      <c r="B204" s="2">
+      <c r="B204">
         <v>203</v>
       </c>
       <c r="C204">
@@ -4915,7 +4923,7 @@
       <c r="A205" s="1">
         <v>42947</v>
       </c>
-      <c r="B205" s="2">
+      <c r="B205">
         <v>204</v>
       </c>
       <c r="C205">
@@ -4938,7 +4946,7 @@
       <c r="A206" s="1">
         <v>42948</v>
       </c>
-      <c r="B206" s="2">
+      <c r="B206">
         <v>205</v>
       </c>
       <c r="C206">
@@ -4961,7 +4969,7 @@
       <c r="A207" s="1">
         <v>42949</v>
       </c>
-      <c r="B207" s="2">
+      <c r="B207">
         <v>206</v>
       </c>
       <c r="C207">
@@ -4984,7 +4992,7 @@
       <c r="A208" s="1">
         <v>42950</v>
       </c>
-      <c r="B208" s="2">
+      <c r="B208">
         <v>207</v>
       </c>
       <c r="C208">
@@ -5007,7 +5015,7 @@
       <c r="A209" s="1">
         <v>42951</v>
       </c>
-      <c r="B209" s="2">
+      <c r="B209">
         <v>208</v>
       </c>
       <c r="C209">
@@ -5030,7 +5038,7 @@
       <c r="A210" s="1">
         <v>42952</v>
       </c>
-      <c r="B210" s="2">
+      <c r="B210">
         <v>209</v>
       </c>
       <c r="C210">
@@ -5053,7 +5061,7 @@
       <c r="A211" s="1">
         <v>42953</v>
       </c>
-      <c r="B211" s="2">
+      <c r="B211">
         <v>210</v>
       </c>
       <c r="C211">
@@ -5076,7 +5084,7 @@
       <c r="A212" s="1">
         <v>42954</v>
       </c>
-      <c r="B212" s="2">
+      <c r="B212">
         <v>211</v>
       </c>
       <c r="C212">
@@ -5099,7 +5107,7 @@
       <c r="A213" s="1">
         <v>42955</v>
       </c>
-      <c r="B213" s="2">
+      <c r="B213">
         <v>212</v>
       </c>
       <c r="C213">
@@ -5122,7 +5130,7 @@
       <c r="A214" s="1">
         <v>42956</v>
       </c>
-      <c r="B214" s="2">
+      <c r="B214">
         <v>213</v>
       </c>
       <c r="C214">
@@ -5145,7 +5153,7 @@
       <c r="A215" s="1">
         <v>42957</v>
       </c>
-      <c r="B215" s="2">
+      <c r="B215">
         <v>214</v>
       </c>
       <c r="C215">
@@ -5168,7 +5176,7 @@
       <c r="A216" s="1">
         <v>42958</v>
       </c>
-      <c r="B216" s="2">
+      <c r="B216">
         <v>215</v>
       </c>
       <c r="C216">
@@ -5191,7 +5199,7 @@
       <c r="A217" s="1">
         <v>42959</v>
       </c>
-      <c r="B217" s="2">
+      <c r="B217">
         <v>216</v>
       </c>
       <c r="C217">
@@ -5214,7 +5222,7 @@
       <c r="A218" s="1">
         <v>42960</v>
       </c>
-      <c r="B218" s="2">
+      <c r="B218">
         <v>217</v>
       </c>
       <c r="C218">
@@ -5237,7 +5245,7 @@
       <c r="A219" s="1">
         <v>42961</v>
       </c>
-      <c r="B219" s="2">
+      <c r="B219">
         <v>218</v>
       </c>
       <c r="C219">
@@ -5260,7 +5268,7 @@
       <c r="A220" s="1">
         <v>42962</v>
       </c>
-      <c r="B220" s="2">
+      <c r="B220">
         <v>219</v>
       </c>
       <c r="C220">
@@ -5283,7 +5291,7 @@
       <c r="A221" s="1">
         <v>42963</v>
       </c>
-      <c r="B221" s="2">
+      <c r="B221">
         <v>220</v>
       </c>
       <c r="C221">
@@ -5306,7 +5314,7 @@
       <c r="A222" s="1">
         <v>42964</v>
       </c>
-      <c r="B222" s="2">
+      <c r="B222">
         <v>221</v>
       </c>
       <c r="C222">
@@ -5329,7 +5337,7 @@
       <c r="A223" s="1">
         <v>42965</v>
       </c>
-      <c r="B223" s="2">
+      <c r="B223">
         <v>222</v>
       </c>
       <c r="C223">
@@ -5352,7 +5360,7 @@
       <c r="A224" s="1">
         <v>42966</v>
       </c>
-      <c r="B224" s="2">
+      <c r="B224">
         <v>223</v>
       </c>
       <c r="C224">
@@ -5375,7 +5383,7 @@
       <c r="A225" s="1">
         <v>42967</v>
       </c>
-      <c r="B225" s="2">
+      <c r="B225">
         <v>224</v>
       </c>
       <c r="C225">
@@ -5398,7 +5406,7 @@
       <c r="A226" s="1">
         <v>42968</v>
       </c>
-      <c r="B226" s="2">
+      <c r="B226">
         <v>225</v>
       </c>
       <c r="C226">
@@ -5421,7 +5429,7 @@
       <c r="A227" s="1">
         <v>42969</v>
       </c>
-      <c r="B227" s="2">
+      <c r="B227">
         <v>226</v>
       </c>
       <c r="C227">
@@ -5444,7 +5452,7 @@
       <c r="A228" s="1">
         <v>42970</v>
       </c>
-      <c r="B228" s="2">
+      <c r="B228">
         <v>227</v>
       </c>
       <c r="C228">
@@ -5467,7 +5475,7 @@
       <c r="A229" s="1">
         <v>42971</v>
       </c>
-      <c r="B229" s="2">
+      <c r="B229">
         <v>228</v>
       </c>
       <c r="C229">
@@ -5490,7 +5498,7 @@
       <c r="A230" s="1">
         <v>42972</v>
       </c>
-      <c r="B230" s="2">
+      <c r="B230">
         <v>229</v>
       </c>
       <c r="C230">
@@ -5513,7 +5521,7 @@
       <c r="A231" s="1">
         <v>42973</v>
       </c>
-      <c r="B231" s="2">
+      <c r="B231">
         <v>230</v>
       </c>
       <c r="C231">
@@ -5536,7 +5544,7 @@
       <c r="A232" s="1">
         <v>42974</v>
       </c>
-      <c r="B232" s="2">
+      <c r="B232">
         <v>231</v>
       </c>
       <c r="C232">
@@ -5559,7 +5567,7 @@
       <c r="A233" s="1">
         <v>42975</v>
       </c>
-      <c r="B233" s="2">
+      <c r="B233">
         <v>232</v>
       </c>
       <c r="C233">
@@ -5582,7 +5590,7 @@
       <c r="A234" s="1">
         <v>42976</v>
       </c>
-      <c r="B234" s="2">
+      <c r="B234">
         <v>233</v>
       </c>
       <c r="C234">
@@ -5605,7 +5613,7 @@
       <c r="A235" s="1">
         <v>42977</v>
       </c>
-      <c r="B235" s="2">
+      <c r="B235">
         <v>234</v>
       </c>
       <c r="C235">
@@ -5628,7 +5636,7 @@
       <c r="A236" s="1">
         <v>42978</v>
       </c>
-      <c r="B236" s="2">
+      <c r="B236">
         <v>235</v>
       </c>
       <c r="C236">
@@ -5651,7 +5659,7 @@
       <c r="A237" s="1">
         <v>42979</v>
       </c>
-      <c r="B237" s="2">
+      <c r="B237">
         <v>236</v>
       </c>
       <c r="C237">
@@ -5674,7 +5682,7 @@
       <c r="A238" s="1">
         <v>42980</v>
       </c>
-      <c r="B238" s="2">
+      <c r="B238">
         <v>237</v>
       </c>
       <c r="C238">
@@ -5697,7 +5705,7 @@
       <c r="A239" s="1">
         <v>42981</v>
       </c>
-      <c r="B239" s="2">
+      <c r="B239">
         <v>238</v>
       </c>
       <c r="C239">
@@ -5720,7 +5728,7 @@
       <c r="A240" s="1">
         <v>42982</v>
       </c>
-      <c r="B240" s="2">
+      <c r="B240">
         <v>239</v>
       </c>
       <c r="C240">
@@ -5743,7 +5751,7 @@
       <c r="A241" s="1">
         <v>42983</v>
       </c>
-      <c r="B241" s="2">
+      <c r="B241">
         <v>240</v>
       </c>
       <c r="C241">
@@ -5766,7 +5774,7 @@
       <c r="A242" s="1">
         <v>42984</v>
       </c>
-      <c r="B242" s="2">
+      <c r="B242">
         <v>241</v>
       </c>
       <c r="C242">
@@ -5789,7 +5797,7 @@
       <c r="A243" s="1">
         <v>42985</v>
       </c>
-      <c r="B243" s="2">
+      <c r="B243">
         <v>242</v>
       </c>
       <c r="C243">
@@ -5812,7 +5820,7 @@
       <c r="A244" s="1">
         <v>42986</v>
       </c>
-      <c r="B244" s="2">
+      <c r="B244">
         <v>243</v>
       </c>
       <c r="C244">
@@ -5835,7 +5843,7 @@
       <c r="A245" s="1">
         <v>42987</v>
       </c>
-      <c r="B245" s="2">
+      <c r="B245">
         <v>244</v>
       </c>
       <c r="C245">
@@ -5858,7 +5866,7 @@
       <c r="A246" s="1">
         <v>42988</v>
       </c>
-      <c r="B246" s="2">
+      <c r="B246">
         <v>245</v>
       </c>
       <c r="C246">
@@ -5881,7 +5889,7 @@
       <c r="A247" s="1">
         <v>42989</v>
       </c>
-      <c r="B247" s="2">
+      <c r="B247">
         <v>246</v>
       </c>
       <c r="C247">
@@ -5904,7 +5912,7 @@
       <c r="A248" s="1">
         <v>42990</v>
       </c>
-      <c r="B248" s="2">
+      <c r="B248">
         <v>247</v>
       </c>
       <c r="C248">
@@ -5927,7 +5935,7 @@
       <c r="A249" s="1">
         <v>42991</v>
       </c>
-      <c r="B249" s="2">
+      <c r="B249">
         <v>248</v>
       </c>
       <c r="C249">
@@ -5950,7 +5958,7 @@
       <c r="A250" s="1">
         <v>42992</v>
       </c>
-      <c r="B250" s="2">
+      <c r="B250">
         <v>249</v>
       </c>
       <c r="C250">
@@ -5973,7 +5981,7 @@
       <c r="A251" s="1">
         <v>42993</v>
       </c>
-      <c r="B251" s="2">
+      <c r="B251">
         <v>250</v>
       </c>
       <c r="C251">
@@ -5996,7 +6004,7 @@
       <c r="A252" s="1">
         <v>42994</v>
       </c>
-      <c r="B252" s="2">
+      <c r="B252">
         <v>251</v>
       </c>
       <c r="C252">
@@ -6019,7 +6027,7 @@
       <c r="A253" s="1">
         <v>42995</v>
       </c>
-      <c r="B253" s="2">
+      <c r="B253">
         <v>252</v>
       </c>
       <c r="C253">
@@ -6042,7 +6050,7 @@
       <c r="A254" s="1">
         <v>42996</v>
       </c>
-      <c r="B254" s="2">
+      <c r="B254">
         <v>253</v>
       </c>
       <c r="C254">
@@ -6065,7 +6073,7 @@
       <c r="A255" s="1">
         <v>42997</v>
       </c>
-      <c r="B255" s="2">
+      <c r="B255">
         <v>254</v>
       </c>
       <c r="C255">
@@ -6088,7 +6096,7 @@
       <c r="A256" s="1">
         <v>42998</v>
       </c>
-      <c r="B256" s="2">
+      <c r="B256">
         <v>255</v>
       </c>
       <c r="C256">
@@ -6111,7 +6119,7 @@
       <c r="A257" s="1">
         <v>42999</v>
       </c>
-      <c r="B257" s="2">
+      <c r="B257">
         <v>256</v>
       </c>
       <c r="C257">
@@ -6134,7 +6142,7 @@
       <c r="A258" s="1">
         <v>43000</v>
       </c>
-      <c r="B258" s="2">
+      <c r="B258">
         <v>257</v>
       </c>
       <c r="C258">
@@ -6157,7 +6165,7 @@
       <c r="A259" s="1">
         <v>43001</v>
       </c>
-      <c r="B259" s="2">
+      <c r="B259">
         <v>258</v>
       </c>
       <c r="C259">
@@ -6180,7 +6188,7 @@
       <c r="A260" s="1">
         <v>43002</v>
       </c>
-      <c r="B260" s="2">
+      <c r="B260">
         <v>259</v>
       </c>
       <c r="C260">
@@ -6203,7 +6211,7 @@
       <c r="A261" s="1">
         <v>43003</v>
       </c>
-      <c r="B261" s="2">
+      <c r="B261">
         <v>260</v>
       </c>
       <c r="C261">
@@ -6226,7 +6234,7 @@
       <c r="A262" s="1">
         <v>43004</v>
       </c>
-      <c r="B262" s="2">
+      <c r="B262">
         <v>261</v>
       </c>
       <c r="C262">
@@ -6249,7 +6257,7 @@
       <c r="A263" s="1">
         <v>43005</v>
       </c>
-      <c r="B263" s="2">
+      <c r="B263">
         <v>262</v>
       </c>
       <c r="C263">
@@ -6272,7 +6280,7 @@
       <c r="A264" s="1">
         <v>43006</v>
       </c>
-      <c r="B264" s="2">
+      <c r="B264">
         <v>263</v>
       </c>
       <c r="C264">
@@ -6295,7 +6303,7 @@
       <c r="A265" s="1">
         <v>43007</v>
       </c>
-      <c r="B265" s="2">
+      <c r="B265">
         <v>264</v>
       </c>
       <c r="C265">
@@ -6318,7 +6326,7 @@
       <c r="A266" s="1">
         <v>43008</v>
       </c>
-      <c r="B266" s="2">
+      <c r="B266">
         <v>265</v>
       </c>
       <c r="C266">
@@ -6341,7 +6349,7 @@
       <c r="A267" s="1">
         <v>43009</v>
       </c>
-      <c r="B267" s="2">
+      <c r="B267">
         <v>266</v>
       </c>
       <c r="C267">
@@ -6364,7 +6372,7 @@
       <c r="A268" s="1">
         <v>43010</v>
       </c>
-      <c r="B268" s="2">
+      <c r="B268">
         <v>267</v>
       </c>
       <c r="C268">
@@ -6387,7 +6395,7 @@
       <c r="A269" s="1">
         <v>43011</v>
       </c>
-      <c r="B269" s="2">
+      <c r="B269">
         <v>268</v>
       </c>
       <c r="C269">
@@ -6410,7 +6418,7 @@
       <c r="A270" s="1">
         <v>43012</v>
       </c>
-      <c r="B270" s="2">
+      <c r="B270">
         <v>269</v>
       </c>
       <c r="C270">
@@ -6433,7 +6441,7 @@
       <c r="A271" s="1">
         <v>43013</v>
       </c>
-      <c r="B271" s="2">
+      <c r="B271">
         <v>270</v>
       </c>
       <c r="C271">
@@ -6456,7 +6464,7 @@
       <c r="A272" s="1">
         <v>43014</v>
       </c>
-      <c r="B272" s="2">
+      <c r="B272">
         <v>271</v>
       </c>
       <c r="C272">
@@ -6479,7 +6487,7 @@
       <c r="A273" s="1">
         <v>43015</v>
       </c>
-      <c r="B273" s="2">
+      <c r="B273">
         <v>272</v>
       </c>
       <c r="C273">
@@ -6502,7 +6510,7 @@
       <c r="A274" s="1">
         <v>43016</v>
       </c>
-      <c r="B274" s="2">
+      <c r="B274">
         <v>273</v>
       </c>
       <c r="C274">
@@ -6525,7 +6533,7 @@
       <c r="A275" s="1">
         <v>43017</v>
       </c>
-      <c r="B275" s="2">
+      <c r="B275">
         <v>274</v>
       </c>
       <c r="C275">
@@ -6548,7 +6556,7 @@
       <c r="A276" s="1">
         <v>43018</v>
       </c>
-      <c r="B276" s="2">
+      <c r="B276">
         <v>275</v>
       </c>
       <c r="C276">
@@ -6571,7 +6579,7 @@
       <c r="A277" s="1">
         <v>43019</v>
       </c>
-      <c r="B277" s="2">
+      <c r="B277">
         <v>276</v>
       </c>
       <c r="C277">
@@ -6594,7 +6602,7 @@
       <c r="A278" s="1">
         <v>43020</v>
       </c>
-      <c r="B278" s="2">
+      <c r="B278">
         <v>277</v>
       </c>
       <c r="C278">
@@ -6617,7 +6625,7 @@
       <c r="A279" s="1">
         <v>43021</v>
       </c>
-      <c r="B279" s="2">
+      <c r="B279">
         <v>278</v>
       </c>
       <c r="C279">
@@ -6640,7 +6648,7 @@
       <c r="A280" s="1">
         <v>43022</v>
       </c>
-      <c r="B280" s="2">
+      <c r="B280">
         <v>279</v>
       </c>
       <c r="C280">
@@ -6663,7 +6671,7 @@
       <c r="A281" s="1">
         <v>43023</v>
       </c>
-      <c r="B281" s="2">
+      <c r="B281">
         <v>280</v>
       </c>
       <c r="C281">
@@ -6686,7 +6694,7 @@
       <c r="A282" s="1">
         <v>43024</v>
       </c>
-      <c r="B282" s="2">
+      <c r="B282">
         <v>281</v>
       </c>
       <c r="C282">
@@ -6709,7 +6717,7 @@
       <c r="A283" s="1">
         <v>43025</v>
       </c>
-      <c r="B283" s="2">
+      <c r="B283">
         <v>282</v>
       </c>
       <c r="C283">
@@ -6732,7 +6740,7 @@
       <c r="A284" s="1">
         <v>43026</v>
       </c>
-      <c r="B284" s="2">
+      <c r="B284">
         <v>283</v>
       </c>
       <c r="C284">
@@ -6755,7 +6763,7 @@
       <c r="A285" s="1">
         <v>43027</v>
       </c>
-      <c r="B285" s="2">
+      <c r="B285">
         <v>284</v>
       </c>
       <c r="C285">
@@ -6778,7 +6786,7 @@
       <c r="A286" s="1">
         <v>43028</v>
       </c>
-      <c r="B286" s="2">
+      <c r="B286">
         <v>285</v>
       </c>
       <c r="C286">
@@ -6801,7 +6809,7 @@
       <c r="A287" s="1">
         <v>43029</v>
       </c>
-      <c r="B287" s="2">
+      <c r="B287">
         <v>286</v>
       </c>
       <c r="C287">
@@ -6824,7 +6832,7 @@
       <c r="A288" s="1">
         <v>43030</v>
       </c>
-      <c r="B288" s="2">
+      <c r="B288">
         <v>287</v>
       </c>
       <c r="C288">
@@ -6847,7 +6855,7 @@
       <c r="A289" s="1">
         <v>43031</v>
       </c>
-      <c r="B289" s="2">
+      <c r="B289">
         <v>288</v>
       </c>
       <c r="C289">
@@ -6870,7 +6878,7 @@
       <c r="A290" s="1">
         <v>43032</v>
       </c>
-      <c r="B290" s="2">
+      <c r="B290">
         <v>289</v>
       </c>
       <c r="C290">
@@ -6893,7 +6901,7 @@
       <c r="A291" s="1">
         <v>43033</v>
       </c>
-      <c r="B291" s="2">
+      <c r="B291">
         <v>290</v>
       </c>
       <c r="C291">
@@ -6916,7 +6924,7 @@
       <c r="A292" s="1">
         <v>43034</v>
       </c>
-      <c r="B292" s="2">
+      <c r="B292">
         <v>291</v>
       </c>
       <c r="C292">
@@ -6939,7 +6947,7 @@
       <c r="A293" s="1">
         <v>43035</v>
       </c>
-      <c r="B293" s="2">
+      <c r="B293">
         <v>292</v>
       </c>
       <c r="C293">
@@ -6962,7 +6970,7 @@
       <c r="A294" s="1">
         <v>43036</v>
       </c>
-      <c r="B294" s="2">
+      <c r="B294">
         <v>293</v>
       </c>
       <c r="C294">
@@ -6985,7 +6993,7 @@
       <c r="A295" s="1">
         <v>43037</v>
       </c>
-      <c r="B295" s="2">
+      <c r="B295">
         <v>294</v>
       </c>
       <c r="C295">
@@ -7008,7 +7016,7 @@
       <c r="A296" s="1">
         <v>43038</v>
       </c>
-      <c r="B296" s="2">
+      <c r="B296">
         <v>295</v>
       </c>
       <c r="C296">
@@ -7031,7 +7039,7 @@
       <c r="A297" s="1">
         <v>43039</v>
       </c>
-      <c r="B297" s="2">
+      <c r="B297">
         <v>296</v>
       </c>
       <c r="C297">
@@ -7054,7 +7062,7 @@
       <c r="A298" s="1">
         <v>43040</v>
       </c>
-      <c r="B298" s="2">
+      <c r="B298">
         <v>297</v>
       </c>
       <c r="C298">
@@ -7077,7 +7085,7 @@
       <c r="A299" s="1">
         <v>43041</v>
       </c>
-      <c r="B299" s="2">
+      <c r="B299">
         <v>298</v>
       </c>
       <c r="C299">
@@ -7100,7 +7108,7 @@
       <c r="A300" s="1">
         <v>43042</v>
       </c>
-      <c r="B300" s="2">
+      <c r="B300">
         <v>299</v>
       </c>
       <c r="C300">
@@ -7123,7 +7131,7 @@
       <c r="A301" s="1">
         <v>43043</v>
       </c>
-      <c r="B301" s="2">
+      <c r="B301">
         <v>300</v>
       </c>
       <c r="C301">
@@ -7146,7 +7154,7 @@
       <c r="A302" s="1">
         <v>43044</v>
       </c>
-      <c r="B302" s="2">
+      <c r="B302">
         <v>301</v>
       </c>
       <c r="C302">
@@ -7169,7 +7177,7 @@
       <c r="A303" s="1">
         <v>43045</v>
       </c>
-      <c r="B303" s="2">
+      <c r="B303">
         <v>302</v>
       </c>
       <c r="C303">
@@ -7192,7 +7200,7 @@
       <c r="A304" s="1">
         <v>43046</v>
       </c>
-      <c r="B304" s="2">
+      <c r="B304">
         <v>303</v>
       </c>
       <c r="C304">
@@ -7215,7 +7223,7 @@
       <c r="A305" s="1">
         <v>43047</v>
       </c>
-      <c r="B305" s="2">
+      <c r="B305">
         <v>304</v>
       </c>
       <c r="C305">
@@ -7238,7 +7246,7 @@
       <c r="A306" s="1">
         <v>43048</v>
       </c>
-      <c r="B306" s="2">
+      <c r="B306">
         <v>305</v>
       </c>
       <c r="C306">
@@ -7261,7 +7269,7 @@
       <c r="A307" s="1">
         <v>43049</v>
       </c>
-      <c r="B307" s="2">
+      <c r="B307">
         <v>306</v>
       </c>
       <c r="C307">
@@ -7284,7 +7292,7 @@
       <c r="A308" s="1">
         <v>43050</v>
       </c>
-      <c r="B308" s="2">
+      <c r="B308">
         <v>307</v>
       </c>
       <c r="C308">
@@ -7307,7 +7315,7 @@
       <c r="A309" s="1">
         <v>43051</v>
       </c>
-      <c r="B309" s="2">
+      <c r="B309">
         <v>308</v>
       </c>
       <c r="C309">
@@ -7330,7 +7338,7 @@
       <c r="A310" s="1">
         <v>43052</v>
       </c>
-      <c r="B310" s="2">
+      <c r="B310">
         <v>309</v>
       </c>
       <c r="C310">
@@ -7353,7 +7361,7 @@
       <c r="A311" s="1">
         <v>43053</v>
       </c>
-      <c r="B311" s="2">
+      <c r="B311">
         <v>310</v>
       </c>
       <c r="C311">
@@ -7376,7 +7384,7 @@
       <c r="A312" s="1">
         <v>43054</v>
       </c>
-      <c r="B312" s="2">
+      <c r="B312">
         <v>311</v>
       </c>
       <c r="C312">
@@ -7399,7 +7407,7 @@
       <c r="A313" s="1">
         <v>43055</v>
       </c>
-      <c r="B313" s="2">
+      <c r="B313">
         <v>312</v>
       </c>
       <c r="C313">
@@ -7422,7 +7430,7 @@
       <c r="A314" s="1">
         <v>43056</v>
       </c>
-      <c r="B314" s="2">
+      <c r="B314">
         <v>313</v>
       </c>
       <c r="C314">
@@ -7445,7 +7453,7 @@
       <c r="A315" s="1">
         <v>43057</v>
       </c>
-      <c r="B315" s="2">
+      <c r="B315">
         <v>314</v>
       </c>
       <c r="C315">
@@ -7468,7 +7476,7 @@
       <c r="A316" s="1">
         <v>43058</v>
       </c>
-      <c r="B316" s="2">
+      <c r="B316">
         <v>315</v>
       </c>
       <c r="C316">
@@ -7491,7 +7499,7 @@
       <c r="A317" s="1">
         <v>43059</v>
       </c>
-      <c r="B317" s="2">
+      <c r="B317">
         <v>316</v>
       </c>
       <c r="C317">
@@ -7514,7 +7522,7 @@
       <c r="A318" s="1">
         <v>43060</v>
       </c>
-      <c r="B318" s="2">
+      <c r="B318">
         <v>317</v>
       </c>
       <c r="C318">
@@ -7537,7 +7545,7 @@
       <c r="A319" s="1">
         <v>43061</v>
       </c>
-      <c r="B319" s="2">
+      <c r="B319">
         <v>318</v>
       </c>
       <c r="C319">
@@ -7560,7 +7568,7 @@
       <c r="A320" s="1">
         <v>43062</v>
       </c>
-      <c r="B320" s="2">
+      <c r="B320">
         <v>319</v>
       </c>
       <c r="C320">
@@ -7583,7 +7591,7 @@
       <c r="A321" s="1">
         <v>43063</v>
       </c>
-      <c r="B321" s="2">
+      <c r="B321">
         <v>320</v>
       </c>
       <c r="C321">
@@ -7606,7 +7614,7 @@
       <c r="A322" s="1">
         <v>43064</v>
       </c>
-      <c r="B322" s="2">
+      <c r="B322">
         <v>321</v>
       </c>
       <c r="C322">
@@ -7629,7 +7637,7 @@
       <c r="A323" s="1">
         <v>43065</v>
       </c>
-      <c r="B323" s="2">
+      <c r="B323">
         <v>322</v>
       </c>
       <c r="C323">
@@ -7652,7 +7660,7 @@
       <c r="A324" s="1">
         <v>43066</v>
       </c>
-      <c r="B324" s="2">
+      <c r="B324">
         <v>323</v>
       </c>
       <c r="C324">
@@ -7675,7 +7683,7 @@
       <c r="A325" s="1">
         <v>43067</v>
       </c>
-      <c r="B325" s="2">
+      <c r="B325">
         <v>324</v>
       </c>
       <c r="C325">
@@ -7698,7 +7706,7 @@
       <c r="A326" s="1">
         <v>43068</v>
       </c>
-      <c r="B326" s="2">
+      <c r="B326">
         <v>325</v>
       </c>
       <c r="C326">
@@ -7721,7 +7729,7 @@
       <c r="A327" s="1">
         <v>43069</v>
       </c>
-      <c r="B327" s="2">
+      <c r="B327">
         <v>326</v>
       </c>
       <c r="C327">
@@ -7744,7 +7752,7 @@
       <c r="A328" s="1">
         <v>43070</v>
       </c>
-      <c r="B328" s="2">
+      <c r="B328">
         <v>327</v>
       </c>
       <c r="C328">
@@ -7767,7 +7775,7 @@
       <c r="A329" s="1">
         <v>43071</v>
       </c>
-      <c r="B329" s="2">
+      <c r="B329">
         <v>328</v>
       </c>
       <c r="C329">
@@ -7790,7 +7798,7 @@
       <c r="A330" s="1">
         <v>43072</v>
       </c>
-      <c r="B330" s="2">
+      <c r="B330">
         <v>329</v>
       </c>
       <c r="C330">
@@ -7813,7 +7821,7 @@
       <c r="A331" s="1">
         <v>43073</v>
       </c>
-      <c r="B331" s="2">
+      <c r="B331">
         <v>330</v>
       </c>
       <c r="C331">
@@ -7836,7 +7844,7 @@
       <c r="A332" s="1">
         <v>43074</v>
       </c>
-      <c r="B332" s="2">
+      <c r="B332">
         <v>331</v>
       </c>
       <c r="C332">
@@ -7859,7 +7867,7 @@
       <c r="A333" s="1">
         <v>43075</v>
       </c>
-      <c r="B333" s="2">
+      <c r="B333">
         <v>332</v>
       </c>
       <c r="C333">
@@ -7882,7 +7890,7 @@
       <c r="A334" s="1">
         <v>43076</v>
       </c>
-      <c r="B334" s="2">
+      <c r="B334">
         <v>333</v>
       </c>
       <c r="C334">
@@ -7905,7 +7913,7 @@
       <c r="A335" s="1">
         <v>43077</v>
       </c>
-      <c r="B335" s="2">
+      <c r="B335">
         <v>334</v>
       </c>
       <c r="C335">
@@ -7928,7 +7936,7 @@
       <c r="A336" s="1">
         <v>43078</v>
       </c>
-      <c r="B336" s="2">
+      <c r="B336">
         <v>335</v>
       </c>
       <c r="C336">
@@ -7951,7 +7959,7 @@
       <c r="A337" s="1">
         <v>43079</v>
       </c>
-      <c r="B337" s="2">
+      <c r="B337">
         <v>336</v>
       </c>
       <c r="C337">
@@ -7974,7 +7982,7 @@
       <c r="A338" s="1">
         <v>43080</v>
       </c>
-      <c r="B338" s="2">
+      <c r="B338">
         <v>337</v>
       </c>
       <c r="C338">
@@ -7997,7 +8005,7 @@
       <c r="A339" s="1">
         <v>43081</v>
       </c>
-      <c r="B339" s="2">
+      <c r="B339">
         <v>338</v>
       </c>
       <c r="C339">
@@ -8020,7 +8028,7 @@
       <c r="A340" s="1">
         <v>43082</v>
       </c>
-      <c r="B340" s="2">
+      <c r="B340">
         <v>339</v>
       </c>
       <c r="C340">
@@ -8043,7 +8051,7 @@
       <c r="A341" s="1">
         <v>43083</v>
       </c>
-      <c r="B341" s="2">
+      <c r="B341">
         <v>340</v>
       </c>
       <c r="C341">
@@ -8066,7 +8074,7 @@
       <c r="A342" s="1">
         <v>43084</v>
       </c>
-      <c r="B342" s="2">
+      <c r="B342">
         <v>341</v>
       </c>
       <c r="C342">
@@ -8089,7 +8097,7 @@
       <c r="A343" s="1">
         <v>43085</v>
       </c>
-      <c r="B343" s="2">
+      <c r="B343">
         <v>342</v>
       </c>
       <c r="C343">
@@ -8112,7 +8120,7 @@
       <c r="A344" s="1">
         <v>43086</v>
       </c>
-      <c r="B344" s="2">
+      <c r="B344">
         <v>343</v>
       </c>
       <c r="C344">
@@ -8135,7 +8143,7 @@
       <c r="A345" s="1">
         <v>43087</v>
       </c>
-      <c r="B345" s="2">
+      <c r="B345">
         <v>344</v>
       </c>
       <c r="C345">
@@ -8158,7 +8166,7 @@
       <c r="A346" s="1">
         <v>43088</v>
       </c>
-      <c r="B346" s="2">
+      <c r="B346">
         <v>345</v>
       </c>
       <c r="C346">
@@ -8181,7 +8189,7 @@
       <c r="A347" s="1">
         <v>43089</v>
       </c>
-      <c r="B347" s="2">
+      <c r="B347">
         <v>346</v>
       </c>
       <c r="C347">
@@ -8204,7 +8212,7 @@
       <c r="A348" s="1">
         <v>43090</v>
       </c>
-      <c r="B348" s="2">
+      <c r="B348">
         <v>347</v>
       </c>
       <c r="C348">
@@ -8227,7 +8235,7 @@
       <c r="A349" s="1">
         <v>43091</v>
       </c>
-      <c r="B349" s="2">
+      <c r="B349">
         <v>348</v>
       </c>
       <c r="C349">
@@ -8250,7 +8258,7 @@
       <c r="A350" s="1">
         <v>43092</v>
       </c>
-      <c r="B350" s="2">
+      <c r="B350">
         <v>349</v>
       </c>
       <c r="C350">
@@ -8273,7 +8281,7 @@
       <c r="A351" s="1">
         <v>43093</v>
       </c>
-      <c r="B351" s="2">
+      <c r="B351">
         <v>350</v>
       </c>
       <c r="C351">
@@ -8296,7 +8304,7 @@
       <c r="A352" s="1">
         <v>43094</v>
       </c>
-      <c r="B352" s="2">
+      <c r="B352">
         <v>351</v>
       </c>
       <c r="C352">
@@ -8319,7 +8327,7 @@
       <c r="A353" s="1">
         <v>43095</v>
       </c>
-      <c r="B353" s="2">
+      <c r="B353">
         <v>352</v>
       </c>
       <c r="C353">
@@ -8342,7 +8350,7 @@
       <c r="A354" s="1">
         <v>43096</v>
       </c>
-      <c r="B354" s="2">
+      <c r="B354">
         <v>353</v>
       </c>
       <c r="C354">
@@ -8365,7 +8373,7 @@
       <c r="A355" s="1">
         <v>43097</v>
       </c>
-      <c r="B355" s="2">
+      <c r="B355">
         <v>354</v>
       </c>
       <c r="C355">
@@ -8388,7 +8396,7 @@
       <c r="A356" s="1">
         <v>43098</v>
       </c>
-      <c r="B356" s="2">
+      <c r="B356">
         <v>355</v>
       </c>
       <c r="C356">
@@ -8411,7 +8419,7 @@
       <c r="A357" s="1">
         <v>43099</v>
       </c>
-      <c r="B357" s="2">
+      <c r="B357">
         <v>356</v>
       </c>
       <c r="C357">
@@ -8434,7 +8442,7 @@
       <c r="A358" s="1">
         <v>43100</v>
       </c>
-      <c r="B358" s="2">
+      <c r="B358">
         <v>357</v>
       </c>
       <c r="C358">
@@ -8457,7 +8465,7 @@
       <c r="A359" s="1">
         <v>43101</v>
       </c>
-      <c r="B359" s="2">
+      <c r="B359">
         <v>358</v>
       </c>
       <c r="C359">
@@ -8480,7 +8488,7 @@
       <c r="A360" s="1">
         <v>43102</v>
       </c>
-      <c r="B360" s="2">
+      <c r="B360">
         <v>359</v>
       </c>
       <c r="C360">
@@ -8503,7 +8511,7 @@
       <c r="A361" s="1">
         <v>43103</v>
       </c>
-      <c r="B361" s="2">
+      <c r="B361">
         <v>360</v>
       </c>
       <c r="C361">
@@ -8526,7 +8534,7 @@
       <c r="A362" s="1">
         <v>43104</v>
       </c>
-      <c r="B362" s="2">
+      <c r="B362">
         <v>361</v>
       </c>
       <c r="C362">
@@ -8549,7 +8557,7 @@
       <c r="A363" s="1">
         <v>43105</v>
       </c>
-      <c r="B363" s="2">
+      <c r="B363">
         <v>362</v>
       </c>
       <c r="C363">
@@ -8572,7 +8580,7 @@
       <c r="A364" s="1">
         <v>43106</v>
       </c>
-      <c r="B364" s="2">
+      <c r="B364">
         <v>363</v>
       </c>
       <c r="C364">
@@ -8595,7 +8603,7 @@
       <c r="A365" s="1">
         <v>43107</v>
       </c>
-      <c r="B365" s="2">
+      <c r="B365">
         <v>364</v>
       </c>
       <c r="C365">
@@ -8618,7 +8626,7 @@
       <c r="A366" s="1">
         <v>43108</v>
       </c>
-      <c r="B366" s="2">
+      <c r="B366">
         <v>365</v>
       </c>
       <c r="C366">
@@ -8641,7 +8649,7 @@
       <c r="A367" s="1">
         <v>43109</v>
       </c>
-      <c r="B367" s="2">
+      <c r="B367">
         <v>366</v>
       </c>
       <c r="C367">
